--- a/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Донецк 130133080.xlsx
+++ b/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Донецк 130133080.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Uaer4\Downloads\Останкино\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино ЗПФ\ostankino_zpf\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BA8C30-4EE7-49A9-8D13-B6AF30B63862}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E56C08D-0575-4FEB-B151-030BB3B84764}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,18 +17,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$23</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$449</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$449</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$448</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$448</definedName>
   </definedNames>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -183,7 +180,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,12 +288,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <name val="Arial Cyr"/>
-      <charset val="204"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -305,13 +296,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -593,13 +577,13 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="4" fontId="18" fillId="2" borderId="1">
+    <xf numFmtId="4" fontId="17" fillId="2" borderId="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -686,8 +670,8 @@
     <xf numFmtId="1" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -708,9 +692,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -742,9 +723,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -769,15 +747,6 @@
     <xf numFmtId="2" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="5" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -799,6 +768,9 @@
     <xf numFmtId="1" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -817,47 +789,7 @@
     <cellStyle name="Обычный 13" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1293,7 +1225,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N1539"/>
+  <dimension ref="A1:N1538"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -1314,15 +1246,17 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="39"/>
-      <c r="E1" s="69" t="s">
+      <c r="D1" s="63">
+        <v>130133080</v>
+      </c>
+      <c r="E1" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="71"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="67"/>
       <c r="K1" s="26">
         <v>130133079</v>
       </c>
@@ -1355,19 +1289,22 @@
       <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="50"/>
+      <c r="D3" s="64">
+        <v>46209</v>
+      </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="68">
-        <v>130133080</v>
+      <c r="F3" s="64">
+        <f>D3+3</f>
+        <v>46212</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="G3" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="71"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="67"/>
       <c r="K3" s="26">
         <v>130133081</v>
       </c>
@@ -1434,10 +1371,10 @@
     </row>
     <row r="8" spans="1:14" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:14" s="13" customFormat="1" ht="47.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="42" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="12" t="s">
@@ -1467,46 +1404,46 @@
       <c r="K9" s="27"/>
     </row>
     <row r="10" spans="1:14" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="46"/>
-      <c r="B10" s="41" t="s">
+      <c r="A10" s="45"/>
+      <c r="B10" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="42"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="41"/>
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="42"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="41"/>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="57">
+      <c r="A12" s="55">
         <v>5897</v>
       </c>
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="48">
+      <c r="D12" s="47">
         <v>1002134615897</v>
       </c>
       <c r="E12" s="23"/>
@@ -1526,27 +1463,25 @@
       <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="57">
+      <c r="A13" s="55">
         <v>6149</v>
       </c>
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="48">
+      <c r="D13" s="47">
         <v>1002131166149</v>
       </c>
-      <c r="E13" s="23">
-        <v>50</v>
-      </c>
+      <c r="E13" s="23"/>
       <c r="F13" s="22">
         <v>0.3</v>
       </c>
       <c r="G13" s="22">
         <f t="shared" ref="G13:G19" si="0">E13*F13</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H13" s="14">
         <v>3.6</v>
@@ -1557,16 +1492,16 @@
       <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="57">
+      <c r="A14" s="55">
         <v>6819</v>
       </c>
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="48">
+      <c r="D14" s="47">
         <v>1002134276819</v>
       </c>
       <c r="E14" s="23"/>
@@ -1586,27 +1521,25 @@
       <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="57">
+      <c r="A15" s="55">
         <v>6202</v>
       </c>
-      <c r="B15" s="52" t="s">
+      <c r="B15" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="48">
+      <c r="D15" s="47">
         <v>1002131186202</v>
       </c>
-      <c r="E15" s="23">
-        <v>30</v>
-      </c>
+      <c r="E15" s="23"/>
       <c r="F15" s="22">
         <v>0.3</v>
       </c>
       <c r="G15" s="22">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H15" s="14">
         <v>3.6</v>
@@ -1617,27 +1550,25 @@
       <c r="J15" s="28"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="57">
+      <c r="A16" s="55">
         <v>6148</v>
       </c>
-      <c r="B16" s="52" t="s">
+      <c r="B16" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="C16" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="48">
+      <c r="D16" s="47">
         <v>1002133376148</v>
       </c>
-      <c r="E16" s="23">
-        <v>30</v>
-      </c>
+      <c r="E16" s="23"/>
       <c r="F16" s="22">
         <v>0.3</v>
       </c>
       <c r="G16" s="22">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H16" s="14">
         <v>3.6</v>
@@ -1648,27 +1579,25 @@
       <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="57">
+      <c r="A17" s="55">
         <v>6209</v>
       </c>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="C17" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="47">
         <v>1002131146209</v>
       </c>
-      <c r="E17" s="23">
-        <v>150</v>
-      </c>
+      <c r="E17" s="23"/>
       <c r="F17" s="22">
         <v>0.35</v>
       </c>
       <c r="G17" s="22">
         <f t="shared" si="0"/>
-        <v>52.5</v>
+        <v>0</v>
       </c>
       <c r="H17" s="14">
         <v>4.2</v>
@@ -1679,27 +1608,25 @@
       <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="57">
+      <c r="A18" s="55">
         <v>6168</v>
       </c>
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="C18" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="51">
         <v>1002131156168</v>
       </c>
-      <c r="E18" s="23">
-        <v>30</v>
-      </c>
+      <c r="E18" s="23"/>
       <c r="F18" s="22">
         <v>0.35</v>
       </c>
       <c r="G18" s="22">
         <f t="shared" si="0"/>
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="H18" s="14">
         <v>4.2</v>
@@ -1707,19 +1634,19 @@
       <c r="I18" s="14">
         <v>120</v>
       </c>
-      <c r="J18" s="56"/>
+      <c r="J18" s="54"/>
     </row>
     <row r="19" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57">
+      <c r="A19" s="55">
         <v>5579</v>
       </c>
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="51">
         <v>1002134275579</v>
       </c>
       <c r="E19" s="23"/>
@@ -1736,30 +1663,28 @@
       <c r="I19" s="14">
         <v>120</v>
       </c>
-      <c r="J19" s="56"/>
+      <c r="J19" s="54"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="51">
+      <c r="A20" s="49">
         <v>5754</v>
       </c>
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="51">
         <v>1002131155754</v>
       </c>
-      <c r="E20" s="23">
-        <v>18</v>
-      </c>
+      <c r="E20" s="23"/>
       <c r="F20" s="22">
         <v>4.5</v>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="53">
         <f>E20</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H20" s="14">
         <v>4.5</v>
@@ -1767,30 +1692,28 @@
       <c r="I20" s="14">
         <v>120</v>
       </c>
-      <c r="J20" s="56"/>
+      <c r="J20" s="54"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="51">
+      <c r="A21" s="49">
         <v>5755</v>
       </c>
-      <c r="B21" s="49" t="s">
+      <c r="B21" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="48">
+      <c r="D21" s="47">
         <v>1002131185755</v>
       </c>
-      <c r="E21" s="23">
-        <v>4.5</v>
-      </c>
+      <c r="E21" s="23"/>
       <c r="F21" s="22">
         <v>4.5</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="53">
         <f>E21</f>
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H21" s="14">
         <v>4.5</v>
@@ -1801,79 +1724,75 @@
       <c r="J21" s="28"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="66"/>
-      <c r="B22" s="73" t="s">
+      <c r="A22" s="61"/>
+      <c r="B22" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="73"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
     </row>
     <row r="23" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="65">
+      <c r="A23" s="60">
         <v>7216</v>
       </c>
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="64">
+      <c r="D23" s="59">
         <v>1002116437216</v>
       </c>
-      <c r="E23" s="62">
-        <v>230</v>
-      </c>
+      <c r="E23" s="57"/>
       <c r="F23" s="22">
         <v>0.7</v>
       </c>
-      <c r="G23" s="55">
+      <c r="G23" s="53">
         <f t="shared" ref="G23" si="1">E23</f>
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="H23" s="14"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="63"/>
-    </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="59"/>
-      <c r="B24" s="60"/>
-      <c r="C24" s="61"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="20"/>
-    </row>
-    <row r="25" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="58"/>
-      <c r="B25" s="44" t="s">
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+    </row>
+    <row r="24" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="56"/>
+      <c r="B24" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="16">
+      <c r="C24" s="15"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="16">
         <f>SUM(E12:E23)</f>
-        <v>542.5</v>
+        <v>0</v>
       </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16">
+      <c r="F24" s="16"/>
+      <c r="G24" s="16">
         <f>SUM(G13:G23)</f>
-        <v>348.5</v>
+        <v>0</v>
       </c>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-    </row>
-    <row r="26" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="35"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="38"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B26" s="35"/>
       <c r="C26" s="17"/>
       <c r="D26" s="38"/>
@@ -16983,23 +16902,13 @@
       <c r="I1536" s="19"/>
       <c r="J1536" s="20"/>
     </row>
-    <row r="1537" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="1537" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1537" s="35"/>
       <c r="C1537" s="17"/>
-      <c r="D1537" s="38"/>
-      <c r="F1537" s="18"/>
-      <c r="G1537" s="18"/>
-      <c r="H1537" s="19"/>
-      <c r="I1537" s="19"/>
-      <c r="J1537" s="20"/>
-    </row>
-    <row r="1538" spans="2:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1538" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1538" s="35"/>
       <c r="C1538" s="17"/>
-    </row>
-    <row r="1539" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B1539" s="35"/>
-      <c r="C1539" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A9:J23" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -17008,16 +16917,6 @@
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="B22:J22"/>
   </mergeCells>
-  <conditionalFormatting sqref="A24">
-    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A24">
-    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A24">
-    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A23">
     <cfRule type="duplicateValues" dxfId="3" priority="1"/>
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>

--- a/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Донецк 130133080.xlsx
+++ b/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Донецк 130133080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино ЗПФ\ostankino_zpf\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E56C08D-0575-4FEB-B151-030BB3B84764}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A099048-F62D-41E3-AEC7-783339392EF9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$448</definedName>
     <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$448</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -583,7 +583,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -723,27 +723,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -752,12 +731,6 @@
     </xf>
     <xf numFmtId="4" fontId="4" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="9" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -779,8 +752,26 @@
     <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -789,7 +780,47 @@
     <cellStyle name="Обычный 13" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1246,17 +1277,17 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="63">
+      <c r="D1" s="54">
         <v>130133080</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="67"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="58"/>
       <c r="K1" s="26">
         <v>130133079</v>
       </c>
@@ -1289,22 +1320,22 @@
       <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="64">
+      <c r="D3" s="55">
         <v>46209</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="64">
+      <c r="F3" s="55">
         <f>D3+3</f>
         <v>46212</v>
       </c>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="67"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="58"/>
       <c r="K3" s="26">
         <v>130133081</v>
       </c>
@@ -1434,7 +1465,7 @@
       <c r="J11" s="41"/>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="55">
+      <c r="A12" s="60">
         <v>5897</v>
       </c>
       <c r="B12" s="48" t="s">
@@ -1463,10 +1494,10 @@
       <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="55">
+      <c r="A13" s="60">
         <v>6149</v>
       </c>
-      <c r="B13" s="50" t="s">
+      <c r="B13" s="48" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="46" t="s">
@@ -1492,10 +1523,10 @@
       <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="55">
+      <c r="A14" s="60">
         <v>6819</v>
       </c>
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="48" t="s">
         <v>26</v>
       </c>
       <c r="C14" s="46" t="s">
@@ -1521,10 +1552,10 @@
       <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="55">
+      <c r="A15" s="60">
         <v>6202</v>
       </c>
-      <c r="B15" s="50" t="s">
+      <c r="B15" s="48" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="46" t="s">
@@ -1550,10 +1581,10 @@
       <c r="J15" s="28"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="55">
+      <c r="A16" s="60">
         <v>6148</v>
       </c>
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="48" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="46" t="s">
@@ -1579,10 +1610,10 @@
       <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="55">
+      <c r="A17" s="60">
         <v>6209</v>
       </c>
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="48" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="46" t="s">
@@ -1608,16 +1639,16 @@
       <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="55">
+      <c r="A18" s="60">
         <v>6168</v>
       </c>
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="48" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="47">
         <v>1002131156168</v>
       </c>
       <c r="E18" s="23"/>
@@ -1634,19 +1665,19 @@
       <c r="I18" s="14">
         <v>120</v>
       </c>
-      <c r="J18" s="54"/>
+      <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="55">
+      <c r="A19" s="60">
         <v>5579</v>
       </c>
-      <c r="B19" s="50" t="s">
+      <c r="B19" s="48" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="47">
         <v>1002134275579</v>
       </c>
       <c r="E19" s="23"/>
@@ -1663,26 +1694,26 @@
       <c r="I19" s="14">
         <v>120</v>
       </c>
-      <c r="J19" s="54"/>
+      <c r="J19" s="28"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="49">
+      <c r="A20" s="61">
         <v>5754</v>
       </c>
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="62" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="47">
         <v>1002131155754</v>
       </c>
       <c r="E20" s="23"/>
       <c r="F20" s="22">
         <v>4.5</v>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="63">
         <f>E20</f>
         <v>0</v>
       </c>
@@ -1692,10 +1723,10 @@
       <c r="I20" s="14">
         <v>120</v>
       </c>
-      <c r="J20" s="54"/>
+      <c r="J20" s="28"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="49">
+      <c r="A21" s="61">
         <v>5755</v>
       </c>
       <c r="B21" s="48" t="s">
@@ -1711,7 +1742,7 @@
       <c r="F21" s="22">
         <v>4.5</v>
       </c>
-      <c r="G21" s="53">
+      <c r="G21" s="63">
         <f>E21</f>
         <v>0</v>
       </c>
@@ -1724,58 +1755,58 @@
       <c r="J21" s="28"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="61"/>
-      <c r="B22" s="69" t="s">
+      <c r="A22" s="52"/>
+      <c r="B22" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="64"/>
     </row>
     <row r="23" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="60">
+      <c r="A23" s="65">
         <v>7216</v>
       </c>
-      <c r="B23" s="62" t="s">
+      <c r="B23" s="53" t="s">
         <v>44</v>
       </c>
       <c r="C23" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="59">
+      <c r="D23" s="66">
         <v>1002116437216</v>
       </c>
-      <c r="E23" s="57"/>
+      <c r="E23" s="50"/>
       <c r="F23" s="22">
         <v>0.7</v>
       </c>
-      <c r="G23" s="53">
-        <f t="shared" ref="G23" si="1">E23</f>
+      <c r="G23" s="63">
+        <f>E23*F23</f>
         <v>0</v>
       </c>
       <c r="H23" s="14"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
     </row>
     <row r="24" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="56"/>
+      <c r="A24" s="49"/>
       <c r="B24" s="43" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="34"/>
       <c r="E24" s="16">
-        <f>SUM(E12:E23)</f>
+        <f>SUM(E10:E23)</f>
         <v>0</v>
       </c>
       <c r="F24" s="16"/>
       <c r="G24" s="16">
-        <f>SUM(G13:G23)</f>
+        <f>SUM(G12:G23)</f>
         <v>0</v>
       </c>
       <c r="H24" s="16"/>
